--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532881</v>
+        <v>128532884</v>
       </c>
       <c r="B6" t="n">
-        <v>91472</v>
+        <v>80217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774845</v>
+        <v>775159</v>
       </c>
       <c r="R6" t="n">
-        <v>7316301</v>
+        <v>7316382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532884</v>
+        <v>128532881</v>
       </c>
       <c r="B7" t="n">
-        <v>80217</v>
+        <v>91472</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775159</v>
+        <v>774845</v>
       </c>
       <c r="R7" t="n">
-        <v>7316382</v>
+        <v>7316301</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532883</v>
       </c>
       <c r="B2" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128532887</v>
       </c>
       <c r="B3" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128532882</v>
       </c>
       <c r="B4" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128532885</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128532884</v>
       </c>
       <c r="B6" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128532881</v>
       </c>
       <c r="B7" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128532886</v>
       </c>
       <c r="B8" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532883</v>
       </c>
       <c r="B2" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532884</v>
+        <v>128532881</v>
       </c>
       <c r="B6" t="n">
-        <v>80221</v>
+        <v>91484</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775159</v>
+        <v>774845</v>
       </c>
       <c r="R6" t="n">
-        <v>7316382</v>
+        <v>7316301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532881</v>
+        <v>128532884</v>
       </c>
       <c r="B7" t="n">
-        <v>91478</v>
+        <v>80221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>774845</v>
+        <v>775159</v>
       </c>
       <c r="R7" t="n">
-        <v>7316301</v>
+        <v>7316382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532883</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128532887</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128532882</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128532885</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128532881</v>
       </c>
       <c r="B6" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128532884</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128532886</v>
       </c>
       <c r="B8" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532883</v>
       </c>
       <c r="B2" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128532881</v>
       </c>
       <c r="B6" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532883</v>
       </c>
       <c r="B2" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128532887</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128532882</v>
       </c>
       <c r="B4" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128532885</v>
       </c>
       <c r="B5" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128532881</v>
       </c>
       <c r="B6" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128532884</v>
       </c>
       <c r="B7" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128532886</v>
       </c>
       <c r="B8" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532881</v>
+        <v>128532884</v>
       </c>
       <c r="B6" t="n">
-        <v>91514</v>
+        <v>80250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774845</v>
+        <v>775159</v>
       </c>
       <c r="R6" t="n">
-        <v>7316301</v>
+        <v>7316382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532884</v>
+        <v>128532881</v>
       </c>
       <c r="B7" t="n">
-        <v>80250</v>
+        <v>91514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775159</v>
+        <v>774845</v>
       </c>
       <c r="R7" t="n">
-        <v>7316382</v>
+        <v>7316301</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532883</v>
       </c>
       <c r="B2" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128532887</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128532882</v>
       </c>
       <c r="B4" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128532885</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532884</v>
+        <v>128532881</v>
       </c>
       <c r="B6" t="n">
-        <v>80250</v>
+        <v>91519</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775159</v>
+        <v>774845</v>
       </c>
       <c r="R6" t="n">
-        <v>7316382</v>
+        <v>7316301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532881</v>
+        <v>128532884</v>
       </c>
       <c r="B7" t="n">
-        <v>91514</v>
+        <v>80254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>774845</v>
+        <v>775159</v>
       </c>
       <c r="R7" t="n">
-        <v>7316301</v>
+        <v>7316382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1314,7 +1314,7 @@
         <v>128532886</v>
       </c>
       <c r="B8" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532883</v>
       </c>
       <c r="B2" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532881</v>
+        <v>128532884</v>
       </c>
       <c r="B6" t="n">
-        <v>91519</v>
+        <v>80254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774845</v>
+        <v>775159</v>
       </c>
       <c r="R6" t="n">
-        <v>7316301</v>
+        <v>7316382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532884</v>
+        <v>128532881</v>
       </c>
       <c r="B7" t="n">
-        <v>80254</v>
+        <v>91524</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775159</v>
+        <v>774845</v>
       </c>
       <c r="R7" t="n">
-        <v>7316382</v>
+        <v>7316301</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532884</v>
+        <v>128532881</v>
       </c>
       <c r="B6" t="n">
-        <v>80254</v>
+        <v>91524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775159</v>
+        <v>774845</v>
       </c>
       <c r="R6" t="n">
-        <v>7316382</v>
+        <v>7316301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532881</v>
+        <v>128532884</v>
       </c>
       <c r="B7" t="n">
-        <v>91524</v>
+        <v>80254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>774845</v>
+        <v>775159</v>
       </c>
       <c r="R7" t="n">
-        <v>7316301</v>
+        <v>7316382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532883</v>
       </c>
       <c r="B2" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128532887</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128532882</v>
       </c>
       <c r="B4" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128532885</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128532881</v>
       </c>
       <c r="B6" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128532884</v>
       </c>
       <c r="B7" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128532886</v>
       </c>
       <c r="B8" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532881</v>
+        <v>128532884</v>
       </c>
       <c r="B6" t="n">
-        <v>91528</v>
+        <v>80258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774845</v>
+        <v>775159</v>
       </c>
       <c r="R6" t="n">
-        <v>7316301</v>
+        <v>7316382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532884</v>
+        <v>128532881</v>
       </c>
       <c r="B7" t="n">
-        <v>80258</v>
+        <v>91528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775159</v>
+        <v>774845</v>
       </c>
       <c r="R7" t="n">
-        <v>7316382</v>
+        <v>7316301</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532883</v>
       </c>
       <c r="B2" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128532887</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128532882</v>
       </c>
       <c r="B4" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128532885</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532884</v>
+        <v>128532881</v>
       </c>
       <c r="B6" t="n">
-        <v>80258</v>
+        <v>91533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775159</v>
+        <v>774845</v>
       </c>
       <c r="R6" t="n">
-        <v>7316382</v>
+        <v>7316301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532881</v>
+        <v>128532884</v>
       </c>
       <c r="B7" t="n">
-        <v>91528</v>
+        <v>80163</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>774845</v>
+        <v>775159</v>
       </c>
       <c r="R7" t="n">
-        <v>7316301</v>
+        <v>7316382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1314,7 +1314,7 @@
         <v>128532886</v>
       </c>
       <c r="B8" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532883</v>
       </c>
       <c r="B2" t="n">
-        <v>91535</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128532887</v>
       </c>
       <c r="B3" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128532882</v>
       </c>
       <c r="B4" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128532885</v>
       </c>
       <c r="B5" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128532884</v>
       </c>
       <c r="B6" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128532881</v>
       </c>
       <c r="B7" t="n">
-        <v>91535</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128532886</v>
       </c>
       <c r="B8" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532884</v>
+        <v>128532881</v>
       </c>
       <c r="B6" t="n">
-        <v>80168</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775159</v>
+        <v>774845</v>
       </c>
       <c r="R6" t="n">
-        <v>7316382</v>
+        <v>7316301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1205,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128532881</v>
+        <v>128532884</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>80168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>774845</v>
+        <v>775159</v>
       </c>
       <c r="R7" t="n">
-        <v>7316301</v>
+        <v>7316382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128532883</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128532887</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>128532882</v>
       </c>
       <c r="B4" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>128532885</v>
       </c>
       <c r="B5" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>128532881</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>91546</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>128532884</v>
       </c>
       <c r="B7" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128532886</v>
       </c>
       <c r="B8" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44704-2025 artfynd.xlsx
+++ b/artfynd/A 44704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128532883</v>
+        <v>128532881</v>
       </c>
       <c r="B2" t="n">
-        <v>91546</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>774966</v>
+        <v>774845</v>
       </c>
       <c r="R2" t="n">
-        <v>7316410</v>
+        <v>7316301</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128532887</v>
+        <v>128532883</v>
       </c>
       <c r="B3" t="n">
-        <v>80140</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775181</v>
+        <v>774966</v>
       </c>
       <c r="R3" t="n">
-        <v>7316404</v>
+        <v>7316410</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128532882</v>
+        <v>128532885</v>
       </c>
       <c r="B4" t="n">
-        <v>80169</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775185</v>
+        <v>775161</v>
       </c>
       <c r="R4" t="n">
-        <v>7316362</v>
+        <v>7316382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128532885</v>
+        <v>128532887</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775161</v>
+        <v>775181</v>
       </c>
       <c r="R5" t="n">
-        <v>7316382</v>
+        <v>7316404</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128532881</v>
+        <v>128532882</v>
       </c>
       <c r="B6" t="n">
-        <v>91546</v>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774845</v>
+        <v>775185</v>
       </c>
       <c r="R6" t="n">
-        <v>7316301</v>
+        <v>7316362</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1208,7 +1208,7 @@
         <v>128532884</v>
       </c>
       <c r="B7" t="n">
-        <v>80169</v>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>128532886</v>
       </c>
       <c r="B8" t="n">
-        <v>80169</v>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
